--- a/vista tablas sabores/Tablas jennifer 1.xlsx
+++ b/vista tablas sabores/Tablas jennifer 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jennm\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Coding\Regente2.0\vista tablas sabores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B12C7F9-0C33-4E7C-8369-B9F7972EDBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91184AF4-A9C9-4BE2-9803-F6D56811FF38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="5" xr2:uid="{7F5D55E8-FB06-4267-82F6-25D719F819CC}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="5" activeTab="7" xr2:uid="{7F5D55E8-FB06-4267-82F6-25D719F819CC}"/>
   </bookViews>
   <sheets>
     <sheet name="productos_jen_example" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,25 @@
     <sheet name="Antojitos" sheetId="8" r:id="rId7"/>
     <sheet name="Sentencias" sheetId="9" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="128">
   <si>
     <t>id</t>
   </si>
@@ -41,9 +54,6 @@
     <t>categoria</t>
   </si>
   <si>
-    <t>costo</t>
-  </si>
-  <si>
     <t>Chileatole</t>
   </si>
   <si>
@@ -203,15 +213,6 @@
     <t>Refresco</t>
   </si>
   <si>
-    <t>variantes</t>
-  </si>
-  <si>
-    <t>sabores de comida</t>
-  </si>
-  <si>
-    <t>Cervezas baratas</t>
-  </si>
-  <si>
     <t>Victoria</t>
   </si>
   <si>
@@ -221,13 +222,7 @@
     <t>Carta blanca</t>
   </si>
   <si>
-    <t>Extras Tepache</t>
-  </si>
-  <si>
     <t>Especial</t>
-  </si>
-  <si>
-    <t>tamaño</t>
   </si>
   <si>
     <t>Mezcales</t>
@@ -436,7 +431,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -574,7 +569,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -752,6 +747,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -915,54 +916,55 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Bueno" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Encabezado 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Encabezado 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Énfasis1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Énfasis2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Énfasis3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Énfasis4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Énfasis5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Énfasis6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Incorrecto" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Notas" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Salida" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Texto de advertencia" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Texto explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -978,7 +980,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1294,13 +1296,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B75E82C-E528-4B01-9A7F-4D0C9570D5D5}">
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D46"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1313,800 +1315,635 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>13.5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9">
-        <v>13.5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10">
-        <v>13.5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12">
         <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13">
         <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14">
         <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <v>250</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16">
         <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17">
         <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18">
         <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19">
         <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20">
         <v>160</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21">
         <v>130</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22">
         <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23">
         <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24">
         <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24">
-        <v>28.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25">
         <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26">
         <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27">
         <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28">
         <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28">
-        <v>22.5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29">
         <v>105</v>
       </c>
       <c r="D29" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30">
         <v>125</v>
       </c>
       <c r="D30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31">
         <v>65</v>
       </c>
       <c r="D31" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32">
         <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>60</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
-      </c>
-      <c r="E35">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
-      </c>
-      <c r="E36">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>85</v>
       </c>
       <c r="D37" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C38">
         <v>170</v>
       </c>
       <c r="D38" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>185</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
-      </c>
-      <c r="E39">
-        <v>55.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40">
         <v>125</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>175</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
-      </c>
-      <c r="E41">
-        <v>52.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42">
         <v>235</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42">
-        <v>70.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>45</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
-      </c>
-      <c r="E43">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C44">
         <v>40</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
-      </c>
-      <c r="E44">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C45">
         <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46">
         <v>40</v>
       </c>
       <c r="D46" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46">
-        <v>12</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2117,70 +1954,70 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF85C2E-9F74-4F05-8977-2B6A70DC9101}">
   <dimension ref="B3:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
         <v>63</v>
-      </c>
-      <c r="D12" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2191,73 +2028,73 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD1BA137-C9B8-4071-8053-142F3278346A}">
   <dimension ref="B2:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>125</v>
-      </c>
-      <c r="D11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D13" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2268,66 +2105,66 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6BDAA6E-EE75-42DD-80E6-2CFEB460EEE4}">
   <dimension ref="B2:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>73</v>
-      </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E13" s="1"/>
     </row>
   </sheetData>
@@ -2338,177 +2175,177 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4B36E22-CBD5-40FA-A44C-9BB30691515A}">
   <dimension ref="B2:C44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C17" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B34" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+      <c r="C36" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>105</v>
       </c>
       <c r="C37" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C43">
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C44">
         <v>90</v>
@@ -2522,470 +2359,470 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9966A34-1C31-42FF-9544-BD31CCC31B0C}">
   <dimension ref="B2:L34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="H9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H11" t="s">
+        <v>102</v>
+      </c>
+      <c r="K11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="C12">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" t="s">
-        <v>92</v>
-      </c>
-      <c r="K10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" t="s">
-        <v>108</v>
-      </c>
-      <c r="H11" t="s">
-        <v>108</v>
-      </c>
-      <c r="K11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12">
-        <v>30</v>
-      </c>
-      <c r="E12" t="s">
-        <v>86</v>
       </c>
       <c r="F12">
         <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I12">
         <v>30</v>
       </c>
       <c r="K12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="L12">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>85</v>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="C13">
         <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F13">
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I13">
         <v>30</v>
       </c>
       <c r="K13" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="L13">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C14">
         <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F14">
         <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I14">
         <v>30</v>
       </c>
       <c r="K14" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="L14">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C15">
         <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F15">
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I15">
         <v>30</v>
       </c>
       <c r="K15" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L15">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>106</v>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="C16">
         <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="I16">
         <v>30</v>
       </c>
       <c r="K16" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C17">
         <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F17">
         <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I17">
         <v>30</v>
       </c>
       <c r="K17" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L17">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C18">
         <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F18">
         <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I18">
         <v>30</v>
       </c>
       <c r="K18" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L18">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C19">
         <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F19">
         <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I19">
         <v>30</v>
       </c>
       <c r="K19" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L19">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>91</v>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="C20">
         <v>30</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F20">
         <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="I20">
         <v>30</v>
       </c>
       <c r="K20" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L20">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K23" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" t="s">
+        <v>97</v>
+      </c>
+      <c r="H24" t="s">
+        <v>97</v>
+      </c>
+      <c r="K24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" t="s">
-        <v>103</v>
-      </c>
-      <c r="K24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
       <c r="E25" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="K25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" t="s">
+        <v>79</v>
+      </c>
+      <c r="H26" t="s">
+        <v>79</v>
+      </c>
+      <c r="K26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" t="s">
+        <v>81</v>
+      </c>
+      <c r="K27" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" t="s">
+        <v>82</v>
+      </c>
+      <c r="H28" t="s">
+        <v>82</v>
+      </c>
+      <c r="K28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" t="s">
+        <v>100</v>
+      </c>
+      <c r="H29" t="s">
+        <v>100</v>
+      </c>
+      <c r="K29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" t="s">
+        <v>83</v>
+      </c>
+      <c r="K30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" t="s">
+        <v>84</v>
+      </c>
+      <c r="H31" t="s">
+        <v>84</v>
+      </c>
+      <c r="K31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" t="s">
+        <v>101</v>
+      </c>
+      <c r="H32" t="s">
+        <v>101</v>
+      </c>
+      <c r="K32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
         <v>85</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E33" t="s">
         <v>85</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H33" t="s">
         <v>85</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K33" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" t="s">
-        <v>87</v>
-      </c>
-      <c r="H27" t="s">
-        <v>87</v>
-      </c>
-      <c r="K27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" t="s">
-        <v>88</v>
-      </c>
-      <c r="H28" t="s">
-        <v>88</v>
-      </c>
-      <c r="K28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>106</v>
-      </c>
-      <c r="E29" t="s">
-        <v>106</v>
-      </c>
-      <c r="H29" t="s">
-        <v>106</v>
-      </c>
-      <c r="K29" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>89</v>
-      </c>
-      <c r="E30" t="s">
-        <v>89</v>
-      </c>
-      <c r="H30" t="s">
-        <v>89</v>
-      </c>
-      <c r="K30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" t="s">
-        <v>90</v>
-      </c>
-      <c r="H31" t="s">
-        <v>90</v>
-      </c>
-      <c r="K31" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>107</v>
-      </c>
-      <c r="E32" t="s">
-        <v>107</v>
-      </c>
-      <c r="H32" t="s">
-        <v>107</v>
-      </c>
-      <c r="K32" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>91</v>
-      </c>
-      <c r="E33" t="s">
-        <v>91</v>
-      </c>
-      <c r="H33" t="s">
-        <v>91</v>
-      </c>
-      <c r="K33" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="E34" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -2996,123 +2833,123 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D7F15C2-6FE1-4A10-B3C8-8464D534F0F3}">
   <dimension ref="B2:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C13">
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
         <v>85</v>
-      </c>
-      <c r="C14">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>91</v>
       </c>
       <c r="C21">
         <v>30</v>
@@ -3126,121 +2963,121 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E7D6FE-AE64-40F2-8DFC-8AAF228A421B}">
   <dimension ref="B2:L16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" t="s">
+        <v>110</v>
+      </c>
+      <c r="H13" t="s">
+        <v>110</v>
+      </c>
+      <c r="K13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" t="s">
-        <v>116</v>
-      </c>
-      <c r="H13" t="s">
-        <v>116</v>
-      </c>
-      <c r="K13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" t="s">
-        <v>62</v>
-      </c>
-      <c r="K14" t="s">
-        <v>117</v>
       </c>
       <c r="L14" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="H15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
